--- a/r5-core-47-sample-organizations/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r5-core-47-sample-organizations/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-11T21:11:59+00:00</t>
+    <t>2026-10-13T04:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-47-sample-organizations/StructureDefinition-at-core-HealthcareService.xlsx
+++ b/r5-core-47-sample-organizations/StructureDefinition-at-core-HealthcareService.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T04:23:07+00:00</t>
+    <t>2026-10-13T10:45:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,7 +621,7 @@
     <t>Collection of specialties handled by the Healthcare service. This is more of a medical term.</t>
   </si>
   <si>
-    <t>extensible</t>
+    <t>preferred</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/core/r5/ValueSet/at-funktionscode-vs</t>
